--- a/documentos/EVALUACIONES MNM 2026.xlsx
+++ b/documentos/EVALUACIONES MNM 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raúl\Dropbox (Personal)\2026\RESPALDO DE BASE DE DATOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720FB67B-2E78-4416-98AF-2D4278C6B55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E841CACA-CE20-43EC-B7F9-71E47AFA8709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <sheet name="EQUIPO" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1" hidden="1">NIVEL_1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2" hidden="1">NIVEL_2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3" hidden="1">NIVEL_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11" hidden="1">NIVEL_1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21" hidden="1">NIVEL_2[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31" hidden="1">NIVEL_3[]</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">EQUIPO!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'NIVEL 1'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'NIVEL 2'!#REF!</definedName>
@@ -92,7 +92,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_11"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -101,7 +101,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_2">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_2"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_21"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -110,7 +110,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="NIVEL_3">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_3"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_EVALUACIONESMNM2024.xlsxNIVEL_31"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="195">
   <si>
     <t>NOMBRE DEL ALUMNO</t>
   </si>
@@ -768,6 +768,72 @@
   <si>
     <t>Nahia Lopez Lopez</t>
   </si>
+  <si>
+    <t>ESTEBAN DE JESUS ZAPATA TORRES</t>
+  </si>
+  <si>
+    <t>Jhon negrete machado</t>
+  </si>
+  <si>
+    <t>Andres Felipe Salcedo Cogollo</t>
+  </si>
+  <si>
+    <t>Andrea barrera de oro</t>
+  </si>
+  <si>
+    <t>Fabián Córdoba Solano</t>
+  </si>
+  <si>
+    <t>Juan Valentín Gantiva Pardo</t>
+  </si>
+  <si>
+    <t>Isabel Sofia Sanmartin Fuentes</t>
+  </si>
+  <si>
+    <t>Laura Sofia Sanmartin Fuentes</t>
+  </si>
+  <si>
+    <t>Lina Marcela giraldo Urrea</t>
+  </si>
+  <si>
+    <t>Emma Isabella Ortega meza</t>
+  </si>
+  <si>
+    <t>Sara Lucia Zapa Reyes</t>
+  </si>
+  <si>
+    <t>Samuel Manrique Diaz</t>
+  </si>
+  <si>
+    <t>Angie Lorena Vega Sepulveda</t>
+  </si>
+  <si>
+    <t>Luz Angelis Ruiz Vega</t>
+  </si>
+  <si>
+    <t>Claudia Milena Ramos González</t>
+  </si>
+  <si>
+    <t>kirley mesa</t>
+  </si>
+  <si>
+    <t>Mariana Theran Rozo</t>
+  </si>
+  <si>
+    <t>Raul Esteban Vargas Brunal</t>
+  </si>
+  <si>
+    <t>Yesica Sanchez</t>
+  </si>
+  <si>
+    <t>Nohelia Margarita Pertuz Alcazar</t>
+  </si>
+  <si>
+    <t>Dania Luz Ortega Martinez</t>
+  </si>
+  <si>
+    <t>Janer Villarreal vergara</t>
+  </si>
 </sst>
 </file>
 
@@ -899,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1016,147 +1082,65 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="76">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1722,6 +1706,561 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2438,425 +2977,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3125,7 +3245,7 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3328,7 +3448,7 @@
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3531,7 +3651,7 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -3934,7 +4054,7 @@
                         <c:v>49</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>63</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4102,7 +4222,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4270,7 +4390,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -4881,7 +5001,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5089,7 +5209,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -5427,7 +5547,7 @@
                         <c:v>49</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>63</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5595,7 +5715,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>39</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5768,7 +5888,7 @@
                         <c:v>18</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -5941,7 +6061,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>8</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -6616,7 +6736,7 @@
                   <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -6802,7 +6922,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>39</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -6975,7 +7095,7 @@
                         <c:v>4</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>5</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7148,7 +7268,7 @@
                         <c:v>18</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>16</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7321,7 +7441,7 @@
                         <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>2</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -7494,7 +7614,7 @@
                         <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v>0</c:v>
+                        <c:v>8</c:v>
                       </c:pt>
                       <c:pt idx="9">
                         <c:v>0</c:v>
@@ -12147,7 +12267,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}" name="Tabla11" displayName="Tabla11" ref="A1:I13" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A1:I13" xr:uid="{DB9236B4-6758-46F5-ACE3-4324EBF03AFC}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -12160,29 +12280,29 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{E45CE681-0F10-4F5F-ABE9-36AD6411F2F4}" name="MESES" dataDxfId="73"/>
+    <tableColumn id="2" xr3:uid="{C45C8DBF-C350-4EAC-B340-B1433B532DF4}" name="T. ALUMNOS" dataDxfId="72">
       <calculatedColumnFormula>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="53">
+    <tableColumn id="3" xr3:uid="{544D14A8-0150-477C-91EB-9C6A53287C61}" name="TOTAL N1" dataDxfId="71">
       <calculatedColumnFormula>COUNTIF('NIVEL 1'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="52">
+    <tableColumn id="4" xr3:uid="{B844FCB1-5911-4097-AC96-E45A77F4EADB}" name="CAMBIO N2" dataDxfId="70">
       <calculatedColumnFormula>COUNTIFS('NIVEL 1'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$N:$N,"CAMBIA A NIVEL 2")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="51">
+    <tableColumn id="6" xr3:uid="{09584C72-C135-48E6-BBF7-7505B75ADFE1}" name="TOTAL N2" dataDxfId="69">
       <calculatedColumnFormula>COUNTIF('NIVEL 2'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="50">
+    <tableColumn id="7" xr3:uid="{050D800C-3210-4B53-B962-4423AD8D7D44}" name="CAMBIO N3" dataDxfId="68">
       <calculatedColumnFormula>COUNTIFS('NIVEL 2'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$N:$N,"CAMBIA A NIVEL 3")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="49">
+    <tableColumn id="9" xr3:uid="{533A7FB5-2283-4C4B-B4C5-7CB89D8F9805}" name="TOTAL N3" dataDxfId="67">
       <calculatedColumnFormula>COUNTIF('NIVEL 3'!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="48">
+    <tableColumn id="10" xr3:uid="{A1B4EC19-A475-44A6-8767-A1367A64797F}" name="A EQUIPO" dataDxfId="66">
       <calculatedColumnFormula>COUNTIFS('NIVEL 3'!$B:$B,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$N:$N,"CAMBIA A EQUIPO")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="47">
+    <tableColumn id="12" xr3:uid="{BB0919BB-10F2-4412-9120-0EF7216850C1}" name="T. EQUIPO" dataDxfId="65">
       <calculatedColumnFormula>COUNTIF(EQUIPO!$B:$B,REPORTE!A2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12191,37 +12311,37 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O161" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74" tableBorderDxfId="73">
-  <autoFilter ref="A2:O161" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}" name="NIVEL_1" displayName="NIVEL_1" ref="A2:O200" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40" tableBorderDxfId="39">
+  <autoFilter ref="A2:O200" xr:uid="{AE1B38D2-F5E0-437E-A0C7-D4FAEDCDAD9F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O135">
     <sortCondition ref="D3:D25"/>
     <sortCondition ref="A3:A25"/>
     <sortCondition ref="F3:F25"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="72">
+    <tableColumn id="15" xr3:uid="{06087576-FB0C-44ED-9CDF-C51BACC66F7B}" name="#" dataDxfId="38">
       <calculatedColumnFormula>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="71">
+    <tableColumn id="1" xr3:uid="{8EF9B412-985A-48AA-9792-B95947050FCB}" name="NIVEL" dataDxfId="37">
       <calculatedColumnFormula>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="70">
+    <tableColumn id="2" xr3:uid="{2E9F9510-35A9-488E-B1DE-D74FC37EE91B}" name="MES" dataDxfId="36">
       <calculatedColumnFormula>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="65"/>
-    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="64"/>
-    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="63"/>
-    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="62"/>
-    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="61"/>
-    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="60"/>
-    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="59">
+    <tableColumn id="3" xr3:uid="{9F822B2A-0A90-4E18-A961-AC7ADB5E33D7}" name="Fecha de Evaluación" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{F1A37849-EC75-4EFB-8761-8B4816148787}" name="NOMBRE DEL ALUMNO" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{75F8F1A3-4C2C-48D8-BDA8-8EDA5D423C89}" name="DOCUMENTO" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{C323AA94-0265-4893-9265-35B1038BBE77}" name="AMBIENTACION" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{508CEACB-AA59-433A-AFBE-23B4CF5354AF}" name="FLOTACION DEFENSIVA" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{596F9D83-7601-4A50-9A71-07FA546F1FDC}" name="PATADA CROL" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{1386C268-2BDD-48F8-9EC7-CB447E9A76B9}" name="PADATA ESPALDA" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{B76B36D4-2E2E-4645-8403-BA569067D6EB}" name="ENS. CROL" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{A284663E-58C2-40EC-80B3-D1F680E97AF3}" name="ENS ESPALDA" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{EA24CD10-C3F1-45CB-A915-9CB5EA29D8A1}" name="SALTO" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{95D67B47-0B42-429F-9EC3-5161FF1E86D0}" name="Pase de Nivel 4,7 ptos" dataDxfId="25">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 1'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="58">
+    <tableColumn id="14" xr3:uid="{20659D21-4226-4F1C-9913-990D646166B3}" name="Cambio de Nivel" dataDxfId="24">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12230,36 +12350,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O97" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
-  <autoFilter ref="A2:O97" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}" name="NIVEL_2" displayName="NIVEL_2" ref="A2:O113" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63">
+  <autoFilter ref="A2:O113" xr:uid="{D3B83B8F-7030-4C6B-865D-1CEF5FF0A135}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:O79">
     <sortCondition ref="A3:A4"/>
     <sortCondition ref="F3:F4"/>
   </sortState>
   <tableColumns count="15">
-    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="44">
+    <tableColumn id="15" xr3:uid="{09B76DB3-82BE-4C0B-B453-BF194A257258}" name="#" dataDxfId="62">
       <calculatedColumnFormula>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{A30C7826-C605-4AD6-9BD1-976B3108B364}" name="NIVEL" dataDxfId="61">
       <calculatedColumnFormula>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{278C7F91-1379-491F-9B18-95B5FB0F5B4C}" name="MES" dataDxfId="60">
       <calculatedColumnFormula>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="31">
+    <tableColumn id="3" xr3:uid="{61734E93-B6EC-4BCE-81B8-694554146D51}" name="Fecha de Evaluación" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{52287499-B96A-4EC4-9C46-4A9605C862D7}" name="NOMBRE DEL ALUMNO" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{0ECA98BC-FB01-4F67-8A05-CB651A1C8B21}" name="DOCUMENTO" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{4E959843-5A00-4667-9538-531D9390ABDE}" name="TECN ESTILO CROL" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{D6B9A5DE-DA9B-48F2-BC77-F1A1DF233559}" name="TECN ESTILO ESPAL" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{3674AFCF-043A-4668-A622-83DFE8ED6907}" name="ENSE EST PECHO" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{4E82D7B2-52CF-420D-97A4-0A59EFC666C9}" name="ENSE EST MARIPOSA" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{BF17361D-FC57-499E-9503-C2F33EB21C88}" name="INI SALIDA OLIMPICA" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{8B1BEFD7-6FF5-425A-89DA-581562D0A38F}" name="50 m LIBRE" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{991D9CFF-9F59-44B7-AA62-F62FE91F51E4}" name="INI VUELTA OLIMPICA" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{1083E4EB-1DAF-41A3-B727-7BF532F1CB2C}" name="Pase de Nivel 4,7 ptos" dataDxfId="49">
       <calculatedColumnFormula>IFERROR(AVERAGE('NIVEL 2'!G3:M3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="30">
+    <tableColumn id="14" xr3:uid="{EA8CA3F6-4262-42A0-A47A-543052CC352E}" name="Cambio de Nivel" dataDxfId="48">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12268,42 +12388,42 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U26" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" tableBorderDxfId="27">
-  <autoFilter ref="A2:U26" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}" name="NIVEL_3" displayName="NIVEL_3" ref="A2:U34" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A2:U34" xr:uid="{1228A722-3B02-41C4-936F-4D7749F95EAB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:U19">
     <sortCondition ref="A3"/>
     <sortCondition ref="F3"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="26">
+    <tableColumn id="20" xr3:uid="{323FD556-7D50-469A-834D-326AE7F31F42}" name="#" dataDxfId="20">
       <calculatedColumnFormula>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{10AF1518-13B3-40F9-A98E-94CD6E53DC3C}" name="NIVEL" dataDxfId="19">
       <calculatedColumnFormula>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{EB57D90D-D066-4E6D-A973-52FAC5B51F0B}" name="MES" dataDxfId="18">
       <calculatedColumnFormula>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="10"/>
-    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="9"/>
-    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="8"/>
-    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{0FF92161-361C-4203-A4D2-423DC120EB57}" name="Fecha de Evaluación" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{717B9D19-3A86-46A2-91B1-EC86BF2E533D}" name="NOMBRE DEL ALUMNO" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{C69B0C8E-7042-4239-BC38-5DE04F3B8AED}" name="DOCUMENTO" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{1EE2B091-87B8-431E-9319-6E87870DA8A7}" name="100m CROL" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{149128A8-27D9-491E-BD3D-385F53877A11}" name="VUELTA OLIMP. CROL" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{124D09B0-F954-4F41-A77B-869A1BDB006E}" name="LLEGADA CROL" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{350D03DD-5253-4CC2-BFB2-33A4611914A5}" name="SALIDA OLIMP. ESPALDA" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{06F7D230-4D74-4E3E-8042-C13E6EA69D7C}" name="100m ESPALDA" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{C7656A52-730D-4608-BED4-BE3F03A2F535}" name="VUELTA OLIMP. ESPALDA" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{826AA493-8CDE-43B4-9D76-F71252CD2636}" name="LLEGADA ESPALDA" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{EA88C99C-8AE3-41D5-88C9-4D1A205AE057}" name="SALIDA OLIMP. MARIPOSA" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{6446B914-DD25-438C-985E-231095C15D34}" name="25m MARIPOSA" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{ADF9866C-0662-48A4-BD02-64795FE4507E}" name="LLEGADA MARIPOSA" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{B9BF3AB6-845A-4D24-8DE1-E6713B1B6A8E}" name="SALIDA OLIMP. PECHO" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{66B4F0A1-9475-49BD-BDF4-157D5AF07759}" name="25m PECHO" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{C4433153-B84C-45D5-9DAA-18C80B367D88}" name="LLEGADA PECHO" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3A6F3CA6-C52F-40C3-9659-D551D3CB8905}" name="Pase de Nivel 4,9 ptos" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(AVERAGE(G3:S3),"-")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="6">
+    <tableColumn id="19" xr3:uid="{A6317C45-4DC3-4C83-B4AE-F03D89924519}" name="Cambio de Nivel" dataDxfId="0">
       <calculatedColumnFormula array="1">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12312,17 +12432,17 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}" name="NIVEL_213" displayName="NIVEL_213" ref="A2:D138" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="A2:D138" xr:uid="{C5681B1A-EC8A-41B9-A9DC-57C6B186CE75}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D33">
     <sortCondition ref="A3"/>
     <sortCondition ref="D3"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{6BE10E98-8110-4B32-B324-956C2A939720}" name="N°" dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{47EC1D0D-C132-491F-995F-583089EB3DC6}" name="NIVEL" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{E3EBB2A9-A349-4F03-8A3C-7C71DFE91475}" name="MES" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{15956556-3BA8-42CE-A623-63D4505D4189}" name="NOMBRE DEL ALUMNO" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12931,27 +13051,27 @@
       </c>
       <c r="B10" s="17">
         <f>SUM(Tabla11[[#This Row],[TOTAL N1]],Tabla11[[#This Row],[TOTAL N2]],Tabla11[[#This Row],[TOTAL N3]],Tabla11[[#This Row],[T. EQUIPO]])</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C10" s="17">
         <f>COUNTIF('NIVEL 1'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D10" s="17">
         <f>COUNTIFS('NIVEL 1'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 1'!$O:$O,"CAMBIA A NIVEL 2")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E10" s="17">
         <f>COUNTIF('NIVEL 2'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F10" s="17">
         <f>COUNTIFS('NIVEL 2'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 2'!$O:$O,"CAMBIA A NIVEL 3")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="17">
         <f>COUNTIF('NIVEL 3'!$C:$C,REPORTE!A10)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H10" s="17">
         <f>COUNTIFS('NIVEL 3'!$C:$C,Tabla11[[#This Row],[MESES]],'NIVEL 3'!$U:$U,"CAMBIA A EQUIPO")</f>
@@ -13091,7 +13211,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O161"/>
+  <dimension ref="A1:O200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" customWidth="1"/>
@@ -21436,6 +21556,2034 @@
       </c>
       <c r="O161" s="18" t="str" cm="1">
         <f t="array" ref="O161">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A162" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B162" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C162" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D162" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E162" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="F162" s="48" t="s">
+        <v>158</v>
+      </c>
+      <c r="G162" s="45">
+        <v>5</v>
+      </c>
+      <c r="H162" s="45">
+        <v>5</v>
+      </c>
+      <c r="I162" s="45">
+        <v>5</v>
+      </c>
+      <c r="J162" s="45">
+        <v>4</v>
+      </c>
+      <c r="K162" s="45">
+        <v>4</v>
+      </c>
+      <c r="L162" s="45">
+        <v>4</v>
+      </c>
+      <c r="M162" s="45">
+        <v>5</v>
+      </c>
+      <c r="N162" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G162:M162),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O162" s="47" t="str" cm="1">
+        <f t="array" ref="O162">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A163" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B163" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C163" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D163" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E163" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="F163" s="44">
+        <v>1035017030</v>
+      </c>
+      <c r="G163" s="45">
+        <v>5</v>
+      </c>
+      <c r="H163" s="45">
+        <v>5</v>
+      </c>
+      <c r="I163" s="45">
+        <v>5</v>
+      </c>
+      <c r="J163" s="45">
+        <v>4</v>
+      </c>
+      <c r="K163" s="45">
+        <v>4</v>
+      </c>
+      <c r="L163" s="45">
+        <v>4</v>
+      </c>
+      <c r="M163" s="45">
+        <v>5</v>
+      </c>
+      <c r="N163" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G163:M163),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O163" s="47" t="str" cm="1">
+        <f t="array" ref="O163">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A164" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B164" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C164" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D164" s="42">
+        <v>46295</v>
+      </c>
+      <c r="E164" s="43" t="s">
+        <v>77</v>
+      </c>
+      <c r="F164" s="44">
+        <v>1068443767</v>
+      </c>
+      <c r="G164" s="45">
+        <v>5</v>
+      </c>
+      <c r="H164" s="45">
+        <v>5</v>
+      </c>
+      <c r="I164" s="45">
+        <v>3</v>
+      </c>
+      <c r="J164" s="45">
+        <v>3</v>
+      </c>
+      <c r="K164" s="45">
+        <v>1</v>
+      </c>
+      <c r="L164" s="45">
+        <v>3</v>
+      </c>
+      <c r="M164" s="45">
+        <v>5</v>
+      </c>
+      <c r="N164" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G164:M164),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O164" s="47" t="str" cm="1">
+        <f t="array" ref="O164">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A165" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B165" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C165" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D165" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E165" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="F165" s="44">
+        <v>1068442748</v>
+      </c>
+      <c r="G165" s="45">
+        <v>5</v>
+      </c>
+      <c r="H165" s="45">
+        <v>2</v>
+      </c>
+      <c r="I165" s="45">
+        <v>2</v>
+      </c>
+      <c r="J165" s="45">
+        <v>2</v>
+      </c>
+      <c r="K165" s="45">
+        <v>2</v>
+      </c>
+      <c r="L165" s="45">
+        <v>2</v>
+      </c>
+      <c r="M165" s="45">
+        <v>1</v>
+      </c>
+      <c r="N165" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G165:M165),"-")</f>
+        <v>2.2857142857142856</v>
+      </c>
+      <c r="O165" s="47" t="str" cm="1">
+        <f t="array" ref="O165">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A166" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B166" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C166" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D166" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E166" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F166" s="44">
+        <v>1233348383</v>
+      </c>
+      <c r="G166" s="45">
+        <v>5</v>
+      </c>
+      <c r="H166" s="45">
+        <v>5</v>
+      </c>
+      <c r="I166" s="45">
+        <v>5</v>
+      </c>
+      <c r="J166" s="45">
+        <v>4</v>
+      </c>
+      <c r="K166" s="45">
+        <v>4</v>
+      </c>
+      <c r="L166" s="45">
+        <v>4</v>
+      </c>
+      <c r="M166" s="45">
+        <v>5</v>
+      </c>
+      <c r="N166" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G166:M166),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O166" s="47" t="str" cm="1">
+        <f t="array" ref="O166">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A167" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B167" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C167" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D167" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E167" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="F167" s="44">
+        <v>1025564047</v>
+      </c>
+      <c r="G167" s="45">
+        <v>5</v>
+      </c>
+      <c r="H167" s="45">
+        <v>5</v>
+      </c>
+      <c r="I167" s="45">
+        <v>5</v>
+      </c>
+      <c r="J167" s="45">
+        <v>4</v>
+      </c>
+      <c r="K167" s="45">
+        <v>5</v>
+      </c>
+      <c r="L167" s="45">
+        <v>4</v>
+      </c>
+      <c r="M167" s="45">
+        <v>5</v>
+      </c>
+      <c r="N167" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G167:M167),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O167" s="47" t="str" cm="1">
+        <f t="array" ref="O167">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A168" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B168" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C168" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D168" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E168" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="F168" s="44">
+        <v>50906315</v>
+      </c>
+      <c r="G168" s="45">
+        <v>5</v>
+      </c>
+      <c r="H168" s="45">
+        <v>4</v>
+      </c>
+      <c r="I168" s="45">
+        <v>4</v>
+      </c>
+      <c r="J168" s="45">
+        <v>2</v>
+      </c>
+      <c r="K168" s="45">
+        <v>3</v>
+      </c>
+      <c r="L168" s="45">
+        <v>2</v>
+      </c>
+      <c r="M168" s="45">
+        <v>3</v>
+      </c>
+      <c r="N168" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G168:M168),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O168" s="47" t="str" cm="1">
+        <f t="array" ref="O168">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B169" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C169" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D169" s="42">
+        <v>46295</v>
+      </c>
+      <c r="E169" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="F169" s="44">
+        <v>1003047136</v>
+      </c>
+      <c r="G169" s="45">
+        <v>5</v>
+      </c>
+      <c r="H169" s="45">
+        <v>5</v>
+      </c>
+      <c r="I169" s="45">
+        <v>5</v>
+      </c>
+      <c r="J169" s="45">
+        <v>4</v>
+      </c>
+      <c r="K169" s="45">
+        <v>4</v>
+      </c>
+      <c r="L169" s="45">
+        <v>3</v>
+      </c>
+      <c r="M169" s="45">
+        <v>5</v>
+      </c>
+      <c r="N169" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G169:M169),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O169" s="47" t="str" cm="1">
+        <f t="array" ref="O169">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A170" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B170" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C170" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D170" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E170" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="F170" s="44">
+        <v>1233040347</v>
+      </c>
+      <c r="G170" s="45">
+        <v>5</v>
+      </c>
+      <c r="H170" s="45">
+        <v>5</v>
+      </c>
+      <c r="I170" s="45">
+        <v>5</v>
+      </c>
+      <c r="J170" s="45">
+        <v>4</v>
+      </c>
+      <c r="K170" s="45">
+        <v>4</v>
+      </c>
+      <c r="L170" s="45">
+        <v>4</v>
+      </c>
+      <c r="M170" s="45">
+        <v>5</v>
+      </c>
+      <c r="N170" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G170:M170),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O170" s="47" t="str" cm="1">
+        <f t="array" ref="O170">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A171" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B171" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C171" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D171" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E171" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="F171" s="44">
+        <v>1138031915</v>
+      </c>
+      <c r="G171" s="45">
+        <v>5</v>
+      </c>
+      <c r="H171" s="45">
+        <v>5</v>
+      </c>
+      <c r="I171" s="45">
+        <v>5</v>
+      </c>
+      <c r="J171" s="45">
+        <v>4</v>
+      </c>
+      <c r="K171" s="45">
+        <v>4</v>
+      </c>
+      <c r="L171" s="45">
+        <v>4</v>
+      </c>
+      <c r="M171" s="45">
+        <v>5</v>
+      </c>
+      <c r="N171" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G171:M171),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O171" s="47" t="str" cm="1">
+        <f t="array" ref="O171">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A172" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B172" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C172" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D172" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E172" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="F172" s="44">
+        <v>25800927</v>
+      </c>
+      <c r="G172" s="45">
+        <v>5</v>
+      </c>
+      <c r="H172" s="45">
+        <v>5</v>
+      </c>
+      <c r="I172" s="45">
+        <v>4</v>
+      </c>
+      <c r="J172" s="45">
+        <v>3</v>
+      </c>
+      <c r="K172" s="45">
+        <v>3</v>
+      </c>
+      <c r="L172" s="45">
+        <v>3</v>
+      </c>
+      <c r="M172" s="45">
+        <v>4</v>
+      </c>
+      <c r="N172" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G172:M172),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O172" s="47" t="str" cm="1">
+        <f t="array" ref="O172">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A173" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B173" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C173" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D173" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E173" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="F173" s="44">
+        <v>1068444855</v>
+      </c>
+      <c r="G173" s="45">
+        <v>5</v>
+      </c>
+      <c r="H173" s="45">
+        <v>3</v>
+      </c>
+      <c r="I173" s="45">
+        <v>3</v>
+      </c>
+      <c r="J173" s="45">
+        <v>3</v>
+      </c>
+      <c r="K173" s="45">
+        <v>2</v>
+      </c>
+      <c r="L173" s="45">
+        <v>2</v>
+      </c>
+      <c r="M173" s="45">
+        <v>4</v>
+      </c>
+      <c r="N173" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G173:M173),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O173" s="47" t="str" cm="1">
+        <f t="array" ref="O173">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A174" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B174" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C174" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D174" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E174" s="43" t="s">
+        <v>154</v>
+      </c>
+      <c r="F174" s="44">
+        <v>1016116812</v>
+      </c>
+      <c r="G174" s="45">
+        <v>5</v>
+      </c>
+      <c r="H174" s="45">
+        <v>5</v>
+      </c>
+      <c r="I174" s="45">
+        <v>5</v>
+      </c>
+      <c r="J174" s="45">
+        <v>5</v>
+      </c>
+      <c r="K174" s="45">
+        <v>5</v>
+      </c>
+      <c r="L174" s="45">
+        <v>5</v>
+      </c>
+      <c r="M174" s="45">
+        <v>5</v>
+      </c>
+      <c r="N174" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G174:M174),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O174" s="47" t="str" cm="1">
+        <f t="array" ref="O174">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A175" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B175" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C175" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D175" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E175" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="F175" s="44">
+        <v>1038128197</v>
+      </c>
+      <c r="G175" s="45">
+        <v>5</v>
+      </c>
+      <c r="H175" s="45">
+        <v>5</v>
+      </c>
+      <c r="I175" s="45">
+        <v>5</v>
+      </c>
+      <c r="J175" s="45">
+        <v>4</v>
+      </c>
+      <c r="K175" s="45">
+        <v>5</v>
+      </c>
+      <c r="L175" s="45">
+        <v>4</v>
+      </c>
+      <c r="M175" s="45">
+        <v>5</v>
+      </c>
+      <c r="N175" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G175:M175),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O175" s="47" t="str" cm="1">
+        <f t="array" ref="O175">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B176" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C176" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D176" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E176" s="43" t="s">
+        <v>166</v>
+      </c>
+      <c r="F176" s="44">
+        <v>1003357893</v>
+      </c>
+      <c r="G176" s="45">
+        <v>5</v>
+      </c>
+      <c r="H176" s="45">
+        <v>5</v>
+      </c>
+      <c r="I176" s="45">
+        <v>5</v>
+      </c>
+      <c r="J176" s="45">
+        <v>5</v>
+      </c>
+      <c r="K176" s="45">
+        <v>5</v>
+      </c>
+      <c r="L176" s="45">
+        <v>4</v>
+      </c>
+      <c r="M176" s="45">
+        <v>5</v>
+      </c>
+      <c r="N176" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G176:M176),"-")</f>
+        <v>4.8571428571428568</v>
+      </c>
+      <c r="O176" s="47" t="str" cm="1">
+        <f t="array" ref="O176">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A177" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B177" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C177" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D177" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E177" s="43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F177" s="44">
+        <v>1138087397</v>
+      </c>
+      <c r="G177" s="45">
+        <v>5</v>
+      </c>
+      <c r="H177" s="45">
+        <v>5</v>
+      </c>
+      <c r="I177" s="45">
+        <v>4</v>
+      </c>
+      <c r="J177" s="45">
+        <v>4</v>
+      </c>
+      <c r="K177" s="45">
+        <v>4</v>
+      </c>
+      <c r="L177" s="45">
+        <v>3</v>
+      </c>
+      <c r="M177" s="45">
+        <v>5</v>
+      </c>
+      <c r="N177" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G177:M177),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O177" s="47" t="str" cm="1">
+        <f t="array" ref="O177">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A178" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B178" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C178" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D178" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E178" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="F178" s="44">
+        <v>1064988851</v>
+      </c>
+      <c r="G178" s="45">
+        <v>5</v>
+      </c>
+      <c r="H178" s="45">
+        <v>5</v>
+      </c>
+      <c r="I178" s="45">
+        <v>4</v>
+      </c>
+      <c r="J178" s="45">
+        <v>3</v>
+      </c>
+      <c r="K178" s="45">
+        <v>4</v>
+      </c>
+      <c r="L178" s="45">
+        <v>3</v>
+      </c>
+      <c r="M178" s="45">
+        <v>5</v>
+      </c>
+      <c r="N178" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G178:M178),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O178" s="47" t="str" cm="1">
+        <f t="array" ref="O178">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A179" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B179" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C179" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D179" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E179" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="F179" s="44">
+        <v>1065006937</v>
+      </c>
+      <c r="G179" s="45">
+        <v>5</v>
+      </c>
+      <c r="H179" s="45">
+        <v>5</v>
+      </c>
+      <c r="I179" s="45">
+        <v>4</v>
+      </c>
+      <c r="J179" s="45">
+        <v>3</v>
+      </c>
+      <c r="K179" s="45">
+        <v>3</v>
+      </c>
+      <c r="L179" s="45">
+        <v>3</v>
+      </c>
+      <c r="M179" s="45">
+        <v>5</v>
+      </c>
+      <c r="N179" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G179:M179),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O179" s="47" t="str" cm="1">
+        <f t="array" ref="O179">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A180" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B180" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C180" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D180" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E180" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="F180" s="44">
+        <v>1067915998</v>
+      </c>
+      <c r="G180" s="45">
+        <v>5</v>
+      </c>
+      <c r="H180" s="45">
+        <v>5</v>
+      </c>
+      <c r="I180" s="45">
+        <v>4</v>
+      </c>
+      <c r="J180" s="45">
+        <v>3</v>
+      </c>
+      <c r="K180" s="45">
+        <v>3</v>
+      </c>
+      <c r="L180" s="45">
+        <v>2</v>
+      </c>
+      <c r="M180" s="45">
+        <v>5</v>
+      </c>
+      <c r="N180" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G180:M180),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O180" s="47" t="str" cm="1">
+        <f t="array" ref="O180">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A181" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B181" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C181" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D181" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E181" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="F181" s="44">
+        <v>1067942556</v>
+      </c>
+      <c r="G181" s="45">
+        <v>5</v>
+      </c>
+      <c r="H181" s="45">
+        <v>5</v>
+      </c>
+      <c r="I181" s="45">
+        <v>5</v>
+      </c>
+      <c r="J181" s="45">
+        <v>4</v>
+      </c>
+      <c r="K181" s="45">
+        <v>5</v>
+      </c>
+      <c r="L181" s="45">
+        <v>4</v>
+      </c>
+      <c r="M181" s="45">
+        <v>5</v>
+      </c>
+      <c r="N181" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G181:M181),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O181" s="47" t="str" cm="1">
+        <f t="array" ref="O181">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A182" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B182" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C182" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D182" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E182" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="F182" s="44">
+        <v>1062427518</v>
+      </c>
+      <c r="G182" s="45">
+        <v>5</v>
+      </c>
+      <c r="H182" s="45">
+        <v>4</v>
+      </c>
+      <c r="I182" s="45">
+        <v>4</v>
+      </c>
+      <c r="J182" s="45">
+        <v>3</v>
+      </c>
+      <c r="K182" s="45">
+        <v>3</v>
+      </c>
+      <c r="L182" s="45">
+        <v>2</v>
+      </c>
+      <c r="M182" s="45">
+        <v>5</v>
+      </c>
+      <c r="N182" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G182:M182),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O182" s="47" t="str" cm="1">
+        <f t="array" ref="O182">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A183" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B183" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C183" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D183" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E183" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="F183" s="44">
+        <v>1067403890</v>
+      </c>
+      <c r="G183" s="45">
+        <v>5</v>
+      </c>
+      <c r="H183" s="45">
+        <v>5</v>
+      </c>
+      <c r="I183" s="45">
+        <v>4</v>
+      </c>
+      <c r="J183" s="45">
+        <v>3</v>
+      </c>
+      <c r="K183" s="45">
+        <v>3</v>
+      </c>
+      <c r="L183" s="45">
+        <v>3</v>
+      </c>
+      <c r="M183" s="45">
+        <v>5</v>
+      </c>
+      <c r="N183" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G183:M183),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O183" s="47" t="str" cm="1">
+        <f t="array" ref="O183">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A184" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B184" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C184" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D184" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E184" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="F184" s="44">
+        <v>1067921862</v>
+      </c>
+      <c r="G184" s="45">
+        <v>5</v>
+      </c>
+      <c r="H184" s="45">
+        <v>5</v>
+      </c>
+      <c r="I184" s="45">
+        <v>4</v>
+      </c>
+      <c r="J184" s="45">
+        <v>3</v>
+      </c>
+      <c r="K184" s="45">
+        <v>4</v>
+      </c>
+      <c r="L184" s="45">
+        <v>3</v>
+      </c>
+      <c r="M184" s="45">
+        <v>5</v>
+      </c>
+      <c r="N184" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G184:M184),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O184" s="47" t="str" cm="1">
+        <f t="array" ref="O184">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A185" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B185" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C185" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D185" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E185" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F185" s="44">
+        <v>1140444770</v>
+      </c>
+      <c r="G185" s="45">
+        <v>5</v>
+      </c>
+      <c r="H185" s="45">
+        <v>4</v>
+      </c>
+      <c r="I185" s="45">
+        <v>3</v>
+      </c>
+      <c r="J185" s="45">
+        <v>3</v>
+      </c>
+      <c r="K185" s="45">
+        <v>3</v>
+      </c>
+      <c r="L185" s="45">
+        <v>2</v>
+      </c>
+      <c r="M185" s="45">
+        <v>5</v>
+      </c>
+      <c r="N185" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G185:M185),"-")</f>
+        <v>3.5714285714285716</v>
+      </c>
+      <c r="O185" s="47" t="str" cm="1">
+        <f t="array" ref="O185">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A186" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B186" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C186" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D186" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E186" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="F186" s="44">
+        <v>1062446371</v>
+      </c>
+      <c r="G186" s="45">
+        <v>5</v>
+      </c>
+      <c r="H186" s="45">
+        <v>5</v>
+      </c>
+      <c r="I186" s="45">
+        <v>4</v>
+      </c>
+      <c r="J186" s="45">
+        <v>3</v>
+      </c>
+      <c r="K186" s="45">
+        <v>3</v>
+      </c>
+      <c r="L186" s="45">
+        <v>3</v>
+      </c>
+      <c r="M186" s="45">
+        <v>5</v>
+      </c>
+      <c r="N186" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G186:M186),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O186" s="47" t="str" cm="1">
+        <f t="array" ref="O186">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A187" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B187" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C187" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D187" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E187" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="F187" s="44">
+        <v>1233342351</v>
+      </c>
+      <c r="G187" s="45">
+        <v>5</v>
+      </c>
+      <c r="H187" s="45">
+        <v>5</v>
+      </c>
+      <c r="I187" s="45">
+        <v>4</v>
+      </c>
+      <c r="J187" s="45">
+        <v>3</v>
+      </c>
+      <c r="K187" s="45">
+        <v>3</v>
+      </c>
+      <c r="L187" s="45">
+        <v>3</v>
+      </c>
+      <c r="M187" s="45">
+        <v>5</v>
+      </c>
+      <c r="N187" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G187:M187),"-")</f>
+        <v>4</v>
+      </c>
+      <c r="O187" s="47" t="str" cm="1">
+        <f t="array" ref="O187">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A188" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B188" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C188" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D188" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E188" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="F188" s="44">
+        <v>1092551898</v>
+      </c>
+      <c r="G188" s="45">
+        <v>5</v>
+      </c>
+      <c r="H188" s="45">
+        <v>3</v>
+      </c>
+      <c r="I188" s="45">
+        <v>3</v>
+      </c>
+      <c r="J188" s="45">
+        <v>2</v>
+      </c>
+      <c r="K188" s="45">
+        <v>2</v>
+      </c>
+      <c r="L188" s="45">
+        <v>2</v>
+      </c>
+      <c r="M188" s="45">
+        <v>3</v>
+      </c>
+      <c r="N188" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G188:M188),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O188" s="47" t="str" cm="1">
+        <f t="array" ref="O188">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A189" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B189" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C189" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D189" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E189" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="F189" s="44">
+        <v>1062988675</v>
+      </c>
+      <c r="G189" s="45">
+        <v>5</v>
+      </c>
+      <c r="H189" s="45">
+        <v>5</v>
+      </c>
+      <c r="I189" s="45">
+        <v>4</v>
+      </c>
+      <c r="J189" s="45">
+        <v>3</v>
+      </c>
+      <c r="K189" s="45">
+        <v>2</v>
+      </c>
+      <c r="L189" s="45">
+        <v>2</v>
+      </c>
+      <c r="M189" s="45">
+        <v>5</v>
+      </c>
+      <c r="N189" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G189:M189),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O189" s="47" t="str" cm="1">
+        <f t="array" ref="O189">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A190" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B190" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C190" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D190" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E190" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="F190" s="44">
+        <v>1069756890</v>
+      </c>
+      <c r="G190" s="45">
+        <v>5</v>
+      </c>
+      <c r="H190" s="45">
+        <v>5</v>
+      </c>
+      <c r="I190" s="45">
+        <v>5</v>
+      </c>
+      <c r="J190" s="45">
+        <v>4</v>
+      </c>
+      <c r="K190" s="45">
+        <v>4</v>
+      </c>
+      <c r="L190" s="45">
+        <v>3</v>
+      </c>
+      <c r="M190" s="45">
+        <v>5</v>
+      </c>
+      <c r="N190" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G190:M190),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O190" s="47" t="str" cm="1">
+        <f t="array" ref="O190">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A191" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B191" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C191" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D191" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E191" s="43" t="s">
+        <v>185</v>
+      </c>
+      <c r="F191" s="44">
+        <v>1003045871</v>
+      </c>
+      <c r="G191" s="45">
+        <v>5</v>
+      </c>
+      <c r="H191" s="45">
+        <v>5</v>
+      </c>
+      <c r="I191" s="45">
+        <v>4</v>
+      </c>
+      <c r="J191" s="45">
+        <v>3</v>
+      </c>
+      <c r="K191" s="45">
+        <v>4</v>
+      </c>
+      <c r="L191" s="45">
+        <v>3</v>
+      </c>
+      <c r="M191" s="45">
+        <v>5</v>
+      </c>
+      <c r="N191" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G191:M191),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O191" s="47" t="str" cm="1">
+        <f t="array" ref="O191">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A192" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B192" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C192" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D192" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E192" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="F192" s="44">
+        <v>1067907634</v>
+      </c>
+      <c r="G192" s="45">
+        <v>5</v>
+      </c>
+      <c r="H192" s="45">
+        <v>5</v>
+      </c>
+      <c r="I192" s="45">
+        <v>5</v>
+      </c>
+      <c r="J192" s="45">
+        <v>4</v>
+      </c>
+      <c r="K192" s="45">
+        <v>4</v>
+      </c>
+      <c r="L192" s="45">
+        <v>3</v>
+      </c>
+      <c r="M192" s="45">
+        <v>5</v>
+      </c>
+      <c r="N192" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G192:M192),"-")</f>
+        <v>4.4285714285714288</v>
+      </c>
+      <c r="O192" s="47" t="str" cm="1">
+        <f t="array" ref="O192">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A193" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B193" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C193" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D193" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E193" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="F193" s="44">
+        <v>1064995647</v>
+      </c>
+      <c r="G193" s="45">
+        <v>5</v>
+      </c>
+      <c r="H193" s="45">
+        <v>5</v>
+      </c>
+      <c r="I193" s="45">
+        <v>4</v>
+      </c>
+      <c r="J193" s="45">
+        <v>3</v>
+      </c>
+      <c r="K193" s="45">
+        <v>3</v>
+      </c>
+      <c r="L193" s="45">
+        <v>2</v>
+      </c>
+      <c r="M193" s="45">
+        <v>5</v>
+      </c>
+      <c r="N193" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G193:M193),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O193" s="47" t="str" cm="1">
+        <f t="array" ref="O193">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A194" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B194" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C194" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D194" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E194" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="F194" s="44">
+        <v>1073978572</v>
+      </c>
+      <c r="G194" s="45">
+        <v>5</v>
+      </c>
+      <c r="H194" s="45">
+        <v>5</v>
+      </c>
+      <c r="I194" s="45">
+        <v>4</v>
+      </c>
+      <c r="J194" s="45">
+        <v>4</v>
+      </c>
+      <c r="K194" s="45">
+        <v>4</v>
+      </c>
+      <c r="L194" s="45">
+        <v>3</v>
+      </c>
+      <c r="M194" s="45">
+        <v>5</v>
+      </c>
+      <c r="N194" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G194:M194),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O194" s="47" t="str" cm="1">
+        <f t="array" ref="O194">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A195" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B195" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C195" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D195" s="42">
+        <v>46295</v>
+      </c>
+      <c r="E195" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="F195" s="44">
+        <v>1067897784</v>
+      </c>
+      <c r="G195" s="45">
+        <v>5</v>
+      </c>
+      <c r="H195" s="45">
+        <v>4</v>
+      </c>
+      <c r="I195" s="45">
+        <v>3</v>
+      </c>
+      <c r="J195" s="45">
+        <v>2</v>
+      </c>
+      <c r="K195" s="45">
+        <v>2</v>
+      </c>
+      <c r="L195" s="45">
+        <v>2</v>
+      </c>
+      <c r="M195" s="45">
+        <v>4</v>
+      </c>
+      <c r="N195" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G195:M195),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O195" s="47" t="str" cm="1">
+        <f t="array" ref="O195">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A196" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B196" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C196" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D196" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E196" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="F196" s="44">
+        <v>1003717063</v>
+      </c>
+      <c r="G196" s="45">
+        <v>5</v>
+      </c>
+      <c r="H196" s="45">
+        <v>5</v>
+      </c>
+      <c r="I196" s="45">
+        <v>4</v>
+      </c>
+      <c r="J196" s="45">
+        <v>3</v>
+      </c>
+      <c r="K196" s="45">
+        <v>4</v>
+      </c>
+      <c r="L196" s="45">
+        <v>3</v>
+      </c>
+      <c r="M196" s="45">
+        <v>5</v>
+      </c>
+      <c r="N196" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G196:M196),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O196" s="47" t="str" cm="1">
+        <f t="array" ref="O196">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A197" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B197" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C197" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D197" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E197" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="F197" s="44">
+        <v>1067915455</v>
+      </c>
+      <c r="G197" s="45">
+        <v>5</v>
+      </c>
+      <c r="H197" s="45">
+        <v>5</v>
+      </c>
+      <c r="I197" s="45">
+        <v>4</v>
+      </c>
+      <c r="J197" s="45">
+        <v>3</v>
+      </c>
+      <c r="K197" s="45">
+        <v>4</v>
+      </c>
+      <c r="L197" s="45">
+        <v>3</v>
+      </c>
+      <c r="M197" s="45">
+        <v>3</v>
+      </c>
+      <c r="N197" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G197:M197),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O197" s="47" t="str" cm="1">
+        <f t="array" ref="O197">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A198" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B198" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C198" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D198" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E198" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="F198" s="44">
+        <v>1073826174</v>
+      </c>
+      <c r="G198" s="45">
+        <v>5</v>
+      </c>
+      <c r="H198" s="45">
+        <v>5</v>
+      </c>
+      <c r="I198" s="45">
+        <v>4</v>
+      </c>
+      <c r="J198" s="45">
+        <v>2</v>
+      </c>
+      <c r="K198" s="45">
+        <v>2</v>
+      </c>
+      <c r="L198" s="45">
+        <v>2</v>
+      </c>
+      <c r="M198" s="45">
+        <v>2</v>
+      </c>
+      <c r="N198" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G198:M198),"-")</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="O198" s="47" t="str" cm="1">
+        <f t="array" ref="O198">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A199" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B199" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C199" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D199" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E199" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="F199" s="44">
+        <v>1065014577</v>
+      </c>
+      <c r="G199" s="45">
+        <v>5</v>
+      </c>
+      <c r="H199" s="45">
+        <v>3</v>
+      </c>
+      <c r="I199" s="45">
+        <v>3</v>
+      </c>
+      <c r="J199" s="45">
+        <v>2</v>
+      </c>
+      <c r="K199" s="45">
+        <v>2</v>
+      </c>
+      <c r="L199" s="45">
+        <v>2</v>
+      </c>
+      <c r="M199" s="45">
+        <v>2</v>
+      </c>
+      <c r="N199" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G199:M199),"-")</f>
+        <v>2.7142857142857144</v>
+      </c>
+      <c r="O199" s="47" t="str" cm="1">
+        <f t="array" ref="O199">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A200" s="40">
+        <f>MONTH(NIVEL_1[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B200" s="41" t="str">
+        <f>IF(NIVEL_1[[#This Row],['#]]&gt;0,"NIVEL 1","")</f>
+        <v>NIVEL 1</v>
+      </c>
+      <c r="C200" s="41" t="str">
+        <f>TEXT(NIVEL_1[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D200" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E200" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="F200" s="44">
+        <v>1063722590</v>
+      </c>
+      <c r="G200" s="45">
+        <v>5</v>
+      </c>
+      <c r="H200" s="45">
+        <v>4</v>
+      </c>
+      <c r="I200" s="45">
+        <v>3</v>
+      </c>
+      <c r="J200" s="45">
+        <v>3</v>
+      </c>
+      <c r="K200" s="45">
+        <v>2</v>
+      </c>
+      <c r="L200" s="45">
+        <v>2</v>
+      </c>
+      <c r="M200" s="45">
+        <v>5</v>
+      </c>
+      <c r="N200" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 1'!G200:M200),"-")</f>
+        <v>3.4285714285714284</v>
+      </c>
+      <c r="O200" s="47" t="str" cm="1">
+        <f t="array" ref="O200">_xlfn.IFS(NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 2",NIVEL_1[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
         <v>-</v>
       </c>
     </row>
@@ -21463,7 +23611,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.44140625" customWidth="1"/>
@@ -26490,6 +28638,838 @@
         <v>-</v>
       </c>
     </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B98" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C98" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D98" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E98" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F98" s="45">
+        <v>1062981643</v>
+      </c>
+      <c r="G98" s="45">
+        <v>5</v>
+      </c>
+      <c r="H98" s="45">
+        <v>5</v>
+      </c>
+      <c r="I98" s="45">
+        <v>3</v>
+      </c>
+      <c r="J98" s="45">
+        <v>4</v>
+      </c>
+      <c r="K98" s="45">
+        <v>4</v>
+      </c>
+      <c r="L98" s="45">
+        <v>5</v>
+      </c>
+      <c r="M98" s="45">
+        <v>3</v>
+      </c>
+      <c r="N98" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G98:M98),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O98" s="50" t="str" cm="1">
+        <f t="array" ref="O98">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B99" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C99" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D99" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E99" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="F99" s="45">
+        <v>1029722943</v>
+      </c>
+      <c r="G99" s="45">
+        <v>5</v>
+      </c>
+      <c r="H99" s="45">
+        <v>5</v>
+      </c>
+      <c r="I99" s="45">
+        <v>4</v>
+      </c>
+      <c r="J99" s="45">
+        <v>4</v>
+      </c>
+      <c r="K99" s="45">
+        <v>4</v>
+      </c>
+      <c r="L99" s="45">
+        <v>5</v>
+      </c>
+      <c r="M99" s="45">
+        <v>5</v>
+      </c>
+      <c r="N99" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G99:M99),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O99" s="50" t="str" cm="1">
+        <f t="array" ref="O99">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B100" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C100" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D100" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E100" s="43" t="s">
+        <v>146</v>
+      </c>
+      <c r="F100" s="45">
+        <v>1067955099</v>
+      </c>
+      <c r="G100" s="45">
+        <v>5</v>
+      </c>
+      <c r="H100" s="45">
+        <v>5</v>
+      </c>
+      <c r="I100" s="45">
+        <v>4</v>
+      </c>
+      <c r="J100" s="45">
+        <v>4</v>
+      </c>
+      <c r="K100" s="45">
+        <v>5</v>
+      </c>
+      <c r="L100" s="45">
+        <v>5</v>
+      </c>
+      <c r="M100" s="45">
+        <v>4</v>
+      </c>
+      <c r="N100" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G100:M100),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O100" s="50" t="str" cm="1">
+        <f t="array" ref="O100">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B101" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C101" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D101" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E101" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="F101" s="45">
+        <v>1142930859</v>
+      </c>
+      <c r="G101" s="45">
+        <v>5</v>
+      </c>
+      <c r="H101" s="45">
+        <v>5</v>
+      </c>
+      <c r="I101" s="45">
+        <v>5</v>
+      </c>
+      <c r="J101" s="45">
+        <v>5</v>
+      </c>
+      <c r="K101" s="45">
+        <v>5</v>
+      </c>
+      <c r="L101" s="45">
+        <v>5</v>
+      </c>
+      <c r="M101" s="45">
+        <v>5</v>
+      </c>
+      <c r="N101" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G101:M101),"-")</f>
+        <v>5</v>
+      </c>
+      <c r="O101" s="50" t="str" cm="1">
+        <f t="array" ref="O101">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B102" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C102" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D102" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E102" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F102" s="45">
+        <v>1067859838</v>
+      </c>
+      <c r="G102" s="45">
+        <v>5</v>
+      </c>
+      <c r="H102" s="45">
+        <v>5</v>
+      </c>
+      <c r="I102" s="45">
+        <v>5</v>
+      </c>
+      <c r="J102" s="45">
+        <v>5</v>
+      </c>
+      <c r="K102" s="45">
+        <v>5</v>
+      </c>
+      <c r="L102" s="45">
+        <v>5</v>
+      </c>
+      <c r="M102" s="45">
+        <v>2</v>
+      </c>
+      <c r="N102" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G102:M102),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O102" s="50" t="str" cm="1">
+        <f t="array" ref="O102">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B103" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C103" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D103" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E103" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F103" s="45">
+        <v>1073817245</v>
+      </c>
+      <c r="G103" s="45">
+        <v>5</v>
+      </c>
+      <c r="H103" s="45">
+        <v>5</v>
+      </c>
+      <c r="I103" s="45">
+        <v>5</v>
+      </c>
+      <c r="J103" s="45">
+        <v>5</v>
+      </c>
+      <c r="K103" s="45">
+        <v>3</v>
+      </c>
+      <c r="L103" s="45">
+        <v>5</v>
+      </c>
+      <c r="M103" s="45">
+        <v>2</v>
+      </c>
+      <c r="N103" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G103:M103),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O103" s="50" t="str" cm="1">
+        <f t="array" ref="O103">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B104" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C104" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D104" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E104" s="43" t="s">
+        <v>148</v>
+      </c>
+      <c r="F104" s="45">
+        <v>1138032406</v>
+      </c>
+      <c r="G104" s="45">
+        <v>5</v>
+      </c>
+      <c r="H104" s="45">
+        <v>5</v>
+      </c>
+      <c r="I104" s="45">
+        <v>5</v>
+      </c>
+      <c r="J104" s="45">
+        <v>4</v>
+      </c>
+      <c r="K104" s="45">
+        <v>3</v>
+      </c>
+      <c r="L104" s="45">
+        <v>5</v>
+      </c>
+      <c r="M104" s="45">
+        <v>2</v>
+      </c>
+      <c r="N104" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G104:M104),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O104" s="50" t="str" cm="1">
+        <f t="array" ref="O104">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B105" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C105" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D105" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E105" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="F105" s="45">
+        <v>1067945529</v>
+      </c>
+      <c r="G105" s="45">
+        <v>5</v>
+      </c>
+      <c r="H105" s="45">
+        <v>5</v>
+      </c>
+      <c r="I105" s="45">
+        <v>4</v>
+      </c>
+      <c r="J105" s="45">
+        <v>5</v>
+      </c>
+      <c r="K105" s="45">
+        <v>5</v>
+      </c>
+      <c r="L105" s="45">
+        <v>5</v>
+      </c>
+      <c r="M105" s="45">
+        <v>1</v>
+      </c>
+      <c r="N105" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G105:M105),"-")</f>
+        <v>4.2857142857142856</v>
+      </c>
+      <c r="O105" s="50" t="str" cm="1">
+        <f t="array" ref="O105">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B106" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C106" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D106" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E106" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="F106" s="45">
+        <v>1138031920</v>
+      </c>
+      <c r="G106" s="45">
+        <v>5</v>
+      </c>
+      <c r="H106" s="45">
+        <v>5</v>
+      </c>
+      <c r="I106" s="45">
+        <v>5</v>
+      </c>
+      <c r="J106" s="45">
+        <v>4</v>
+      </c>
+      <c r="K106" s="45">
+        <v>5</v>
+      </c>
+      <c r="L106" s="45">
+        <v>5</v>
+      </c>
+      <c r="M106" s="45">
+        <v>4</v>
+      </c>
+      <c r="N106" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G106:M106),"-")</f>
+        <v>4.7142857142857144</v>
+      </c>
+      <c r="O106" s="50" t="str" cm="1">
+        <f t="array" ref="O106">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>CAMBIA A NIVEL 3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B107" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C107" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D107" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E107" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="F107" s="45">
+        <v>1103755851</v>
+      </c>
+      <c r="G107" s="45">
+        <v>4</v>
+      </c>
+      <c r="H107" s="45">
+        <v>4</v>
+      </c>
+      <c r="I107" s="45">
+        <v>3</v>
+      </c>
+      <c r="J107" s="45">
+        <v>3</v>
+      </c>
+      <c r="K107" s="45">
+        <v>2</v>
+      </c>
+      <c r="L107" s="45">
+        <v>3</v>
+      </c>
+      <c r="M107" s="45">
+        <v>1</v>
+      </c>
+      <c r="N107" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G107:M107),"-")</f>
+        <v>2.8571428571428572</v>
+      </c>
+      <c r="O107" s="50" t="str" cm="1">
+        <f t="array" ref="O107">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B108" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C108" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D108" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E108" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="F108" s="45">
+        <v>1062438398</v>
+      </c>
+      <c r="G108" s="45">
+        <v>5</v>
+      </c>
+      <c r="H108" s="45">
+        <v>5</v>
+      </c>
+      <c r="I108" s="45">
+        <v>4</v>
+      </c>
+      <c r="J108" s="45">
+        <v>3</v>
+      </c>
+      <c r="K108" s="45">
+        <v>4</v>
+      </c>
+      <c r="L108" s="45">
+        <v>5</v>
+      </c>
+      <c r="M108" s="45">
+        <v>3</v>
+      </c>
+      <c r="N108" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G108:M108),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O108" s="50" t="str" cm="1">
+        <f t="array" ref="O108">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B109" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C109" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D109" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E109" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="F109" s="45">
+        <v>1065443120</v>
+      </c>
+      <c r="G109" s="45">
+        <v>5</v>
+      </c>
+      <c r="H109" s="45">
+        <v>4</v>
+      </c>
+      <c r="I109" s="45">
+        <v>3</v>
+      </c>
+      <c r="J109" s="45">
+        <v>4</v>
+      </c>
+      <c r="K109" s="45">
+        <v>5</v>
+      </c>
+      <c r="L109" s="45">
+        <v>5</v>
+      </c>
+      <c r="M109" s="45">
+        <v>3</v>
+      </c>
+      <c r="N109" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G109:M109),"-")</f>
+        <v>4.1428571428571432</v>
+      </c>
+      <c r="O109" s="50" t="str" cm="1">
+        <f t="array" ref="O109">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B110" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C110" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D110" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E110" s="43" t="s">
+        <v>150</v>
+      </c>
+      <c r="F110" s="45">
+        <v>1001897545</v>
+      </c>
+      <c r="G110" s="45">
+        <v>5</v>
+      </c>
+      <c r="H110" s="45">
+        <v>5</v>
+      </c>
+      <c r="I110" s="45">
+        <v>3</v>
+      </c>
+      <c r="J110" s="45">
+        <v>5</v>
+      </c>
+      <c r="K110" s="45">
+        <v>5</v>
+      </c>
+      <c r="L110" s="45">
+        <v>5</v>
+      </c>
+      <c r="M110" s="45">
+        <v>4</v>
+      </c>
+      <c r="N110" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G110:M110),"-")</f>
+        <v>4.5714285714285712</v>
+      </c>
+      <c r="O110" s="50" t="str" cm="1">
+        <f t="array" ref="O110">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B111" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C111" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D111" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E111" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="F111" s="45">
+        <v>1062535690</v>
+      </c>
+      <c r="G111" s="45">
+        <v>4</v>
+      </c>
+      <c r="H111" s="45">
+        <v>4</v>
+      </c>
+      <c r="I111" s="45">
+        <v>3</v>
+      </c>
+      <c r="J111" s="45">
+        <v>4</v>
+      </c>
+      <c r="K111" s="45">
+        <v>4</v>
+      </c>
+      <c r="L111" s="45">
+        <v>5</v>
+      </c>
+      <c r="M111" s="45">
+        <v>2</v>
+      </c>
+      <c r="N111" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G111:M111),"-")</f>
+        <v>3.7142857142857144</v>
+      </c>
+      <c r="O111" s="50" t="str" cm="1">
+        <f t="array" ref="O111">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B112" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C112" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D112" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E112" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="F112" s="45">
+        <v>1062440681</v>
+      </c>
+      <c r="G112" s="45">
+        <v>5</v>
+      </c>
+      <c r="H112" s="45">
+        <v>4</v>
+      </c>
+      <c r="I112" s="45">
+        <v>4</v>
+      </c>
+      <c r="J112" s="45">
+        <v>3</v>
+      </c>
+      <c r="K112" s="45">
+        <v>4</v>
+      </c>
+      <c r="L112" s="45">
+        <v>5</v>
+      </c>
+      <c r="M112" s="45">
+        <v>2</v>
+      </c>
+      <c r="N112" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G112:M112),"-")</f>
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="O112" s="50" t="str" cm="1">
+        <f t="array" ref="O112">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A113" s="45">
+        <f>MONTH(NIVEL_2[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B113" s="49" t="str">
+        <f>IF(NIVEL_2[[#This Row],['#]]&gt;0,"NIVEL 2","")</f>
+        <v>NIVEL 2</v>
+      </c>
+      <c r="C113" s="49" t="str">
+        <f>TEXT(NIVEL_2[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D113" s="42">
+        <v>46293</v>
+      </c>
+      <c r="E113" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="F113" s="45">
+        <v>1017126695</v>
+      </c>
+      <c r="G113" s="45">
+        <v>5</v>
+      </c>
+      <c r="H113" s="45">
+        <v>4</v>
+      </c>
+      <c r="I113" s="45">
+        <v>3</v>
+      </c>
+      <c r="J113" s="45">
+        <v>3</v>
+      </c>
+      <c r="K113" s="45">
+        <v>3</v>
+      </c>
+      <c r="L113" s="45">
+        <v>4</v>
+      </c>
+      <c r="M113" s="45">
+        <v>1</v>
+      </c>
+      <c r="N113" s="46">
+        <f>IFERROR(AVERAGE('NIVEL 2'!G113:M113),"-")</f>
+        <v>3.2857142857142856</v>
+      </c>
+      <c r="O113" s="50" t="str" cm="1">
+        <f t="array" ref="O113">_xlfn.IFS(NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]="-","-",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&gt;=4.7,"CAMBIA A NIVEL 3",NIVEL_2[[#This Row],[Pase de Nivel 4,7 ptos]]&lt;=4.7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -26514,7 +29494,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" customWidth="1"/>
@@ -28302,6 +31282,566 @@
       </c>
       <c r="U26" s="32" t="str" cm="1">
         <f t="array" ref="U26">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B27" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C27" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D27" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="55">
+        <v>1027663882</v>
+      </c>
+      <c r="G27" s="55">
+        <v>5</v>
+      </c>
+      <c r="H27" s="55">
+        <v>5</v>
+      </c>
+      <c r="I27" s="55">
+        <v>5</v>
+      </c>
+      <c r="J27" s="55">
+        <v>5</v>
+      </c>
+      <c r="K27" s="55">
+        <v>4</v>
+      </c>
+      <c r="L27" s="55">
+        <v>4</v>
+      </c>
+      <c r="M27" s="55">
+        <v>5</v>
+      </c>
+      <c r="N27" s="55">
+        <v>5</v>
+      </c>
+      <c r="O27" s="55">
+        <v>5</v>
+      </c>
+      <c r="P27" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="55">
+        <v>4</v>
+      </c>
+      <c r="R27" s="55">
+        <v>5</v>
+      </c>
+      <c r="S27" s="55">
+        <v>5</v>
+      </c>
+      <c r="T27" s="56">
+        <f t="shared" ref="T27:T34" si="2">IFERROR(AVERAGE(G27:S27),"-")</f>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="U27" s="57" t="str" cm="1">
+        <f t="array" ref="U27">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B28" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C28" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D28" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E28" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" s="55">
+        <v>1062980565</v>
+      </c>
+      <c r="G28" s="55">
+        <v>5</v>
+      </c>
+      <c r="H28" s="55">
+        <v>5</v>
+      </c>
+      <c r="I28" s="55">
+        <v>5</v>
+      </c>
+      <c r="J28" s="55">
+        <v>5</v>
+      </c>
+      <c r="K28" s="55">
+        <v>4</v>
+      </c>
+      <c r="L28" s="55">
+        <v>3</v>
+      </c>
+      <c r="M28" s="55">
+        <v>5</v>
+      </c>
+      <c r="N28" s="55">
+        <v>4</v>
+      </c>
+      <c r="O28" s="55">
+        <v>4</v>
+      </c>
+      <c r="P28" s="55">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="55">
+        <v>3</v>
+      </c>
+      <c r="R28" s="55">
+        <v>4</v>
+      </c>
+      <c r="S28" s="55">
+        <v>5</v>
+      </c>
+      <c r="T28" s="56">
+        <f t="shared" si="2"/>
+        <v>4.3076923076923075</v>
+      </c>
+      <c r="U28" s="57" t="str" cm="1">
+        <f t="array" ref="U28">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B29" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C29" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D29" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="55">
+        <v>1062539643</v>
+      </c>
+      <c r="G29" s="55">
+        <v>5</v>
+      </c>
+      <c r="H29" s="55">
+        <v>5</v>
+      </c>
+      <c r="I29" s="55">
+        <v>5</v>
+      </c>
+      <c r="J29" s="55">
+        <v>5</v>
+      </c>
+      <c r="K29" s="55">
+        <v>4</v>
+      </c>
+      <c r="L29" s="55">
+        <v>4</v>
+      </c>
+      <c r="M29" s="55">
+        <v>5</v>
+      </c>
+      <c r="N29" s="55">
+        <v>5</v>
+      </c>
+      <c r="O29" s="55">
+        <v>5</v>
+      </c>
+      <c r="P29" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="55">
+        <v>4</v>
+      </c>
+      <c r="R29" s="55">
+        <v>5</v>
+      </c>
+      <c r="S29" s="55">
+        <v>5</v>
+      </c>
+      <c r="T29" s="56">
+        <f t="shared" si="2"/>
+        <v>4.7692307692307692</v>
+      </c>
+      <c r="U29" s="57" t="str" cm="1">
+        <f t="array" ref="U29">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B30" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C30" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D30" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E30" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="55">
+        <v>1138032549</v>
+      </c>
+      <c r="G30" s="55">
+        <v>5</v>
+      </c>
+      <c r="H30" s="55">
+        <v>4</v>
+      </c>
+      <c r="I30" s="55">
+        <v>5</v>
+      </c>
+      <c r="J30" s="55">
+        <v>4</v>
+      </c>
+      <c r="K30" s="55">
+        <v>4</v>
+      </c>
+      <c r="L30" s="55">
+        <v>3</v>
+      </c>
+      <c r="M30" s="55">
+        <v>5</v>
+      </c>
+      <c r="N30" s="55">
+        <v>4</v>
+      </c>
+      <c r="O30" s="55">
+        <v>4</v>
+      </c>
+      <c r="P30" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q30" s="55">
+        <v>3</v>
+      </c>
+      <c r="R30" s="55">
+        <v>4</v>
+      </c>
+      <c r="S30" s="55">
+        <v>5</v>
+      </c>
+      <c r="T30" s="56">
+        <f t="shared" si="2"/>
+        <v>4.2307692307692308</v>
+      </c>
+      <c r="U30" s="57" t="str" cm="1">
+        <f t="array" ref="U30">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B31" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C31" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D31" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="F31" s="55">
+        <v>1007822238</v>
+      </c>
+      <c r="G31" s="55">
+        <v>5</v>
+      </c>
+      <c r="H31" s="55">
+        <v>5</v>
+      </c>
+      <c r="I31" s="55">
+        <v>5</v>
+      </c>
+      <c r="J31" s="55">
+        <v>5</v>
+      </c>
+      <c r="K31" s="55">
+        <v>4</v>
+      </c>
+      <c r="L31" s="55">
+        <v>4</v>
+      </c>
+      <c r="M31" s="55">
+        <v>5</v>
+      </c>
+      <c r="N31" s="55">
+        <v>5</v>
+      </c>
+      <c r="O31" s="55">
+        <v>5</v>
+      </c>
+      <c r="P31" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="55">
+        <v>3</v>
+      </c>
+      <c r="R31" s="55">
+        <v>3</v>
+      </c>
+      <c r="S31" s="55">
+        <v>5</v>
+      </c>
+      <c r="T31" s="56">
+        <f t="shared" si="2"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U31" s="57" t="str" cm="1">
+        <f t="array" ref="U31">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B32" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C32" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D32" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="55">
+        <v>1068439668</v>
+      </c>
+      <c r="G32" s="55">
+        <v>5</v>
+      </c>
+      <c r="H32" s="55">
+        <v>5</v>
+      </c>
+      <c r="I32" s="55">
+        <v>5</v>
+      </c>
+      <c r="J32" s="55">
+        <v>5</v>
+      </c>
+      <c r="K32" s="55">
+        <v>4</v>
+      </c>
+      <c r="L32" s="55">
+        <v>3</v>
+      </c>
+      <c r="M32" s="55">
+        <v>5</v>
+      </c>
+      <c r="N32" s="55">
+        <v>5</v>
+      </c>
+      <c r="O32" s="55">
+        <v>5</v>
+      </c>
+      <c r="P32" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="55">
+        <v>3</v>
+      </c>
+      <c r="R32" s="55">
+        <v>4</v>
+      </c>
+      <c r="S32" s="55">
+        <v>5</v>
+      </c>
+      <c r="T32" s="56">
+        <f t="shared" si="2"/>
+        <v>4.5384615384615383</v>
+      </c>
+      <c r="U32" s="57" t="str" cm="1">
+        <f t="array" ref="U32">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B33" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C33" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D33" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="55">
+        <v>1140444971</v>
+      </c>
+      <c r="G33" s="55">
+        <v>5</v>
+      </c>
+      <c r="H33" s="55">
+        <v>2</v>
+      </c>
+      <c r="I33" s="55">
+        <v>5</v>
+      </c>
+      <c r="J33" s="55">
+        <v>4</v>
+      </c>
+      <c r="K33" s="55">
+        <v>4</v>
+      </c>
+      <c r="L33" s="55">
+        <v>2</v>
+      </c>
+      <c r="M33" s="55">
+        <v>5</v>
+      </c>
+      <c r="N33" s="55">
+        <v>4</v>
+      </c>
+      <c r="O33" s="55">
+        <v>5</v>
+      </c>
+      <c r="P33" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="55">
+        <v>3</v>
+      </c>
+      <c r="R33" s="55">
+        <v>4</v>
+      </c>
+      <c r="S33" s="55">
+        <v>5</v>
+      </c>
+      <c r="T33" s="56">
+        <f t="shared" si="2"/>
+        <v>4.0769230769230766</v>
+      </c>
+      <c r="U33" s="57" t="str" cm="1">
+        <f t="array" ref="U33">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34" s="51">
+        <f>MONTH(NIVEL_3[[#This Row],[Fecha de Evaluación]])</f>
+        <v>9</v>
+      </c>
+      <c r="B34" s="41" t="str">
+        <f>IF(NIVEL_3[[#This Row],['#]]&gt;0,"NIVEL 3","")</f>
+        <v>NIVEL 3</v>
+      </c>
+      <c r="C34" s="52" t="str">
+        <f>TEXT(NIVEL_3[[#This Row],[Fecha de Evaluación]],"MMMM")</f>
+        <v>septiembre</v>
+      </c>
+      <c r="D34" s="53">
+        <v>46293</v>
+      </c>
+      <c r="E34" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="55">
+        <v>8203609</v>
+      </c>
+      <c r="G34" s="55">
+        <v>5</v>
+      </c>
+      <c r="H34" s="55">
+        <v>5</v>
+      </c>
+      <c r="I34" s="55">
+        <v>5</v>
+      </c>
+      <c r="J34" s="55">
+        <v>5</v>
+      </c>
+      <c r="K34" s="55">
+        <v>4</v>
+      </c>
+      <c r="L34" s="55">
+        <v>4</v>
+      </c>
+      <c r="M34" s="55">
+        <v>5</v>
+      </c>
+      <c r="N34" s="55">
+        <v>5</v>
+      </c>
+      <c r="O34" s="55">
+        <v>5</v>
+      </c>
+      <c r="P34" s="55">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="55">
+        <v>3</v>
+      </c>
+      <c r="R34" s="55">
+        <v>5</v>
+      </c>
+      <c r="S34" s="55">
+        <v>5</v>
+      </c>
+      <c r="T34" s="56">
+        <f t="shared" si="2"/>
+        <v>4.6923076923076925</v>
+      </c>
+      <c r="U34" s="57" t="str" cm="1">
+        <f t="array" ref="U34">_xlfn.IFS(NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]="-","-",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&gt;=4.9,"CAMBIA A EQUIPO",NIVEL_3[[#This Row],[Pase de Nivel 4,9 ptos]]&lt;=4.9,"-")</f>
         <v>-</v>
       </c>
     </row>
